--- a/practice/answers/q085.xlsx
+++ b/practice/answers/q085.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,7 +87,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -8565,7 +8567,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" dataOnRows="0" dataCaption="Values" showError="0" showMissing="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="0" showItems="1" editData="0" disableFieldList="0" showCalcMbrs="1" visualTotals="1" showMultipleLabel="1" showDataDropDown="1" showDrill="1" printDrill="0" showMemberPropertyTips="1" showDataTips="1" enableWizard="1" enableDrill="1" enableFieldProperties="1" preserveFormatting="1" useAutoFormatting="1" pageWrap="0" pageOverThenDown="0" subtotalHiddenItems="0" rowGrandTotals="1" colGrandTotals="0" fieldPrintTitles="0" itemPrintTitles="1" mergeItem="0" showDropZones="1" createdVersion="8" indent="0" showEmptyRow="0" showEmptyCol="0" showHeaders="1" compact="0" outline="1" outlineData="1" compactData="0" published="0" gridDropZones="0" immersive="1" multipleFieldFilters="0" chartFormat="0" fieldListSortAscending="0" mdxSubqueries="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" r:id="rId1">
-  <location ref="A3:B103" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:C104" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField showDropDowns="1" compact="1" outline="1" subtotalTop="1" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" itemPageCount="10" sortType="manual" defaultSubtotal="1"/>
     <pivotField axis="axisRow" showDropDowns="1" compact="1" outline="1" subtotalTop="1" dragToRow="1" dragToCol="1" dragToPage="1" dragToData="1" dragOff="1" showAll="0" topAutoShow="1" itemPageCount="10" sortType="manual" defaultSubtotal="0">
@@ -8982,11 +8984,20 @@
       <x v="0"/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i t="data" r="0" i="0"/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i t="data" r="0" i="0">
+      <x v="0"/>
+    </i>
+    <i t="data" r="0" i="1">
+      <x v="1"/>
+    </i>
   </colItems>
-  <dataFields count="1">
+  <dataFields count="2">
     <dataField name="Average of Yield_bu_ac" fld="5" subtotal="average" showDataAs="normal" baseField="0" baseItem="0" numFmtId="2"/>
+    <dataField name="Count of Yield_bu_ac" fld="5" subtotal="count" showDataAs="normal" baseField="0" baseItem="0" numFmtId="3"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
 </pivotTableDefinition>
@@ -34829,15 +34840,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Q85 — Municipality (2023)</t>
         </is>
@@ -34846,999 +34858,1311 @@
     <row r="2"/>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Municipality</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Average of Yield_bu_ac</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ALEXANDER</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>84.2</v>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Count of Yield_bu_ac</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALONSA</t>
+          <t>ALEXANDER</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>55.7</v>
+        <v>84.2</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARGYLE</t>
+          <t>ALONSA</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>62.325</v>
+        <v>55.7</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARMSTRONG</t>
+          <t>ARGYLE</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>46.3</v>
+        <v>62.325</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BIFROST-RIVERTON</t>
+          <t>ARMSTRONG</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>64.32857142857144</v>
+        <v>46.3</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BOISSEVAIN-MORTON</t>
+          <t>BIFROST-RIVERTON</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>69.02857142857142</v>
+        <v>64.32857142857144</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRENDA-WASKADA</t>
+          <t>BOISSEVAIN-MORTON</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>52.96666666666667</v>
+        <v>69.02857142857142</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BROKENHEAD</t>
+          <t>BRENDA-WASKADA</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>60.82857142857143</v>
+        <v>52.96666666666667</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CARTIER</t>
+          <t>BROKENHEAD</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>71.39999999999999</v>
+        <v>60.82857142857143</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CARTWRIGHT-ROBLIN</t>
+          <t>CARTIER</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>55</v>
+        <v>71.39999999999999</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CLANWILLIAM-ERICKSON</t>
+          <t>CARTWRIGHT-ROBLIN</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>59.65</v>
+        <v>55</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COLDWELL</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
+          <t>CLANWILLIAM-ERICKSON</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CORNWALLIS</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>63</v>
+          <t>COLDWELL</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DAUPHIN</t>
+          <t>CORNWALLIS</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>58.27142857142857</v>
+        <v>63</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DELORAINE-WINCHESTER</t>
+          <t>DAUPHIN</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>70.34</v>
+        <v>58.27142857142857</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DESALABERRY</t>
+          <t>DELORAINE-WINCHESTER</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>50.6</v>
+        <v>70.34</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DUFFERIN</t>
+          <t>DESALABERRY</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>51.02500000000001</v>
+        <v>50.6</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EAST ST PAUL</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
+          <t>DUFFERIN</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>51.02500000000001</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ELLICE-ARCHIE</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>57.02</v>
+          <t>EAST ST PAUL</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ELTON</t>
+          <t>ELLICE-ARCHIE</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>77.47999999999999</v>
+        <v>57.02</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EMERSON-FRANKLIN</t>
+          <t>ELTON</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>73.3</v>
+        <v>77.47999999999999</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ETHELBERT</t>
+          <t>EMERSON-FRANKLIN</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>43.76666666666666</v>
+        <v>73.3</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FISHER</t>
+          <t>ETHELBERT</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>58.93333333333334</v>
+        <v>43.76666666666666</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GILBERT PLAINS</t>
+          <t>FISHER</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>62.78571428571428</v>
+        <v>58.93333333333334</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GIMLI</t>
+          <t>GILBERT PLAINS</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>73.3</v>
+        <v>62.78571428571428</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GLENBORO-SOUTH CYPRESS</t>
+          <t>GIMLI</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>58.95</v>
+        <v>73.3</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GLENELLA-LANSDOWNE</t>
+          <t>GLENBORO-SOUTH CYPRESS</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>56.25</v>
+        <v>58.95</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GRAHAMDALE</t>
+          <t>GLENELLA-LANSDOWNE</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>46.2</v>
+        <v>56.25</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GRANDVIEW</t>
+          <t>GRAHAMDALE</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>63.02499999999999</v>
+        <v>46.2</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GRASSLAND</t>
+          <t>GRANDVIEW</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>61.76666666666666</v>
+        <v>63.02499999999999</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GREY</t>
+          <t>GRASSLAND</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>57.25</v>
+        <v>61.76666666666666</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HAMIOTA</t>
+          <t>GREY</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>73</v>
+        <v>57.25</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HANOVER</t>
+          <t>HAMIOTA</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>72.03333333333335</v>
+        <v>73</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HARRISON PARK</t>
+          <t>HANOVER</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>63.94285714285714</v>
+        <v>72.03333333333335</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HEADINGLEY</t>
+          <t>HARRISON PARK</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>68.2</v>
+        <v>63.94285714285714</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HILLSBURG-ROBLIN-SHELL RIVER</t>
+          <t>HEADINGLEY</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>65.53999999999999</v>
+        <v>68.2</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KELSEY</t>
+          <t>HILLSBURG-ROBLIN-SHELL RIVER</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>40.85</v>
+        <v>65.53999999999999</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KILLARNEY-TURTLE MTN</t>
+          <t>KELSEY</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>63.38571428571428</v>
+        <v>40.85</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LA BROQUERIE</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n"/>
+          <t>KILLARNEY-TURTLE MTN</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>63.38571428571428</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LAC DU BONNET</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n">
-        <v>68.7</v>
+          <t>LA BROQUERIE</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LAKESHORE</t>
+          <t>LAC DU BONNET</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>49.05</v>
+        <v>68.7</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LORNE</t>
+          <t>LAKESHORE</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>59.78000000000001</v>
+        <v>49.05</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LOUISE</t>
+          <t>LORNE</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>64.92500000000001</v>
+        <v>59.78000000000001</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MACDONALD</t>
+          <t>LOUISE</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>50.59999999999999</v>
+        <v>64.92500000000001</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MCCREARY</t>
+          <t>MACDONALD</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>61.7</v>
+        <v>50.59999999999999</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MINITONAS-BOWSMAN</t>
+          <t>MCCREARY</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>64.88</v>
+        <v>61.7</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MINTO-ODANAH</t>
+          <t>MINITONAS-BOWSMAN</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>76.36</v>
+        <v>64.88</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MONTCALM</t>
+          <t>MINTO-ODANAH</t>
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>54.53333333333334</v>
+        <v>76.36</v>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MORRIS</t>
+          <t>MONTCALM</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>38.6375</v>
+        <v>54.53333333333334</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MOSSEY RIVER</t>
+          <t>MORRIS</t>
         </is>
       </c>
       <c r="B54" s="6" t="n">
-        <v>32.25</v>
+        <v>38.6375</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MOUNTAIN</t>
+          <t>MOSSEY RIVER</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>59.775</v>
+        <v>32.25</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NORFOLK-TREHERNE</t>
+          <t>MOUNTAIN</t>
         </is>
       </c>
       <c r="B56" s="6" t="n">
-        <v>61.03333333333334</v>
+        <v>59.775</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NORTH CYPRESS-LANGFORD</t>
+          <t>NORFOLK-TREHERNE</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>73.78333333333333</v>
+        <v>61.03333333333334</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NORTH NORFOLK</t>
+          <t>NORTH CYPRESS-LANGFORD</t>
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>55.75</v>
+        <v>73.78333333333333</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OAKLAND-WAWANESA</t>
+          <t>NORTH NORFOLK</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>70.02000000000001</v>
+        <v>55.75</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>OAKVIEW</t>
+          <t>OAKLAND-WAWANESA</t>
         </is>
       </c>
       <c r="B60" s="6" t="n">
-        <v>70.09999999999999</v>
+        <v>70.02000000000001</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PEMBINA</t>
+          <t>OAKVIEW</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>64.11666666666667</v>
+        <v>70.09999999999999</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PINEY</t>
+          <t>PEMBINA</t>
         </is>
       </c>
       <c r="B62" s="6" t="n">
-        <v>57.1</v>
+        <v>64.11666666666667</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PIPESTONE</t>
+          <t>PINEY</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>48.875</v>
+        <v>57.1</v>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PORTAGE LA PRAIRIE</t>
+          <t>PIPESTONE</t>
         </is>
       </c>
       <c r="B64" s="6" t="n">
-        <v>66.8</v>
+        <v>48.875</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PRAIRIE LAKES</t>
+          <t>PORTAGE LA PRAIRIE</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>64.325</v>
+        <v>66.8</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PRAIRIE VIEW</t>
+          <t>PRAIRIE LAKES</t>
         </is>
       </c>
       <c r="B66" s="6" t="n">
-        <v>64.45555555555556</v>
+        <v>64.325</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>REYNOLDS</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="n"/>
+          <t>PRAIRIE VIEW</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>64.45555555555556</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RHINELAND</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="n">
-        <v>63.90000000000001</v>
+          <t>REYNOLDS</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RIDING MOUNTAIN WEST</t>
+          <t>RHINELAND</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>69.51000000000001</v>
+        <v>63.90000000000001</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RITCHOT</t>
+          <t>RIDING MOUNTAIN WEST</t>
         </is>
       </c>
       <c r="B70" s="6" t="n">
-        <v>60.8</v>
+        <v>69.51000000000001</v>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RIVERDALE</t>
+          <t>RITCHOT</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>64.92</v>
+        <v>60.8</v>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ROCKWOOD</t>
+          <t>RIVERDALE</t>
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>54.7</v>
+        <v>64.92</v>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ROLAND</t>
+          <t>ROCKWOOD</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>50.25</v>
+        <v>54.7</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ROSEDALE</t>
+          <t>ROLAND</t>
         </is>
       </c>
       <c r="B74" s="6" t="n">
-        <v>72.84</v>
+        <v>50.25</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ROSSBURN</t>
+          <t>ROSEDALE</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>61.88571428571428</v>
+        <v>72.84</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ROSSER</t>
+          <t>ROSSBURN</t>
         </is>
       </c>
       <c r="B76" s="6" t="n">
-        <v>64.175</v>
+        <v>61.88571428571428</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RUSSELL-BINSCARTH</t>
+          <t>ROSSER</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>66.37142857142858</v>
+        <v>64.175</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SIFTON</t>
+          <t>RUSSELL-BINSCARTH</t>
         </is>
       </c>
       <c r="B78" s="6" t="n">
-        <v>42.15000000000001</v>
+        <v>66.37142857142858</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SOURIS-GLENWOOD</t>
+          <t>SIFTON</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>64.75</v>
+        <v>42.15000000000001</v>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SPRINGFIELD</t>
+          <t>SOURIS-GLENWOOD</t>
         </is>
       </c>
       <c r="B80" s="6" t="n">
-        <v>74.6857142857143</v>
+        <v>64.75</v>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ST. ANDREWS</t>
+          <t>SPRINGFIELD</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>65.21666666666667</v>
+        <v>74.6857142857143</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ST. CLEMENTS</t>
+          <t>ST. ANDREWS</t>
         </is>
       </c>
       <c r="B82" s="6" t="n">
-        <v>66.55</v>
+        <v>65.21666666666667</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ST. FRANCIS XAVIER</t>
+          <t>ST. CLEMENTS</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>68.09999999999999</v>
+        <v>66.55</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ST. LAURENT</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="n"/>
+          <t>ST. FRANCIS XAVIER</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STANLEY</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="n">
-        <v>61.52500000000001</v>
+          <t>ST. LAURENT</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STE. ANNE</t>
+          <t>STANLEY</t>
         </is>
       </c>
       <c r="B86" s="6" t="n">
-        <v>54.4</v>
+        <v>61.52500000000001</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STE. ROSE</t>
+          <t>STE. ANNE</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>65.00000000000001</v>
+        <v>54.4</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STUARTBURN</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="n"/>
+          <t>STE. ROSE</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n">
+        <v>65.00000000000001</v>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SWAN VALLEY WEST</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="n">
-        <v>60.45</v>
+          <t>STUARTBURN</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TACHE</t>
+          <t>SWAN VALLEY WEST</t>
         </is>
       </c>
       <c r="B90" s="6" t="n">
-        <v>65.90000000000001</v>
+        <v>60.45</v>
+      </c>
+      <c r="C90" s="7" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>THOMPSON</t>
+          <t>TACHE</t>
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>68.96666666666665</v>
+        <v>65.90000000000001</v>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TWO BORDERS</t>
+          <t>THOMPSON</t>
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>41.06</v>
+        <v>68.96666666666665</v>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>UNORG TERRITORY</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="n"/>
+          <t>TWO BORDERS</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VICTORIA</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="n">
-        <v>59.15</v>
+          <t>UNORG TERRITORY</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>WALLACE-WOODWORTH</t>
+          <t>VICTORIA</t>
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>55.95000000000001</v>
+        <v>59.15</v>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>WEST INTERLAKE</t>
+          <t>WALLACE-WOODWORTH</t>
         </is>
       </c>
       <c r="B96" s="6" t="n">
-        <v>22</v>
+        <v>55.95000000000001</v>
+      </c>
+      <c r="C96" s="7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>WEST ST. PAUL</t>
+          <t>WEST INTERLAKE</t>
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>61.7</v>
+        <v>22</v>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>WESTLAKE-GLADSTONE</t>
+          <t>WEST ST. PAUL</t>
         </is>
       </c>
       <c r="B98" s="6" t="n">
-        <v>58.48333333333333</v>
+        <v>61.7</v>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>WHITEHEAD</t>
+          <t>WESTLAKE-GLADSTONE</t>
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>64.175</v>
+        <v>58.48333333333333</v>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>WHITEMOUTH</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="n"/>
+          <t>WHITEHEAD</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="n">
+        <v>64.175</v>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>WINNIPEG</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="n">
-        <v>60.8</v>
+          <t>WHITEMOUTH</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>WOODLANDS</t>
+          <t>WINNIPEG</t>
         </is>
       </c>
       <c r="B102" s="6" t="n">
-        <v>58.5</v>
+        <v>60.8</v>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>WOODLANDS</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>YELLOWHEAD</t>
         </is>
       </c>
-      <c r="B103" s="6" t="n">
+      <c r="B104" s="6" t="n">
         <v>73.27777777777777</v>
       </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="C104" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B104" s="7" t="n">
+      <c r="B105" s="8" t="n">
         <v>61.41678486997637</v>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>423</v>
       </c>
     </row>
   </sheetData>
